--- a/analysis/gear_testing_2026/data/2026_gear_testing_gear_log.xlsx
+++ b/analysis/gear_testing_2026/data/2026_gear_testing_gear_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sean.rohan\Work\afsc\trawlmetrics\analysis\gear_testing_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BAC259-1697-4FCA-93DF-B51388F242CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6246530E-CB3E-4C2D-979F-6D6BE471BAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{089E5EFC-D55F-4765-BF86-ADAEB5ED3FEB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="12">
   <si>
     <t>haul</t>
   </si>
@@ -60,6 +60,21 @@
   </si>
   <si>
     <t>depth_treatment</t>
+  </si>
+  <si>
+    <t>half-bobbin</t>
+  </si>
+  <si>
+    <t>bridle_junction</t>
+  </si>
+  <si>
+    <t>bare</t>
+  </si>
+  <si>
+    <t>120 kg weight+swivel</t>
+  </si>
+  <si>
+    <t>120 kg weight</t>
   </si>
 </sst>
 </file>
@@ -431,10 +446,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7790C114-90D1-4BD8-8B71-C43774970C09}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -450,8 +469,11 @@
       <c r="E1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>500</v>
       </c>
@@ -467,8 +489,11 @@
       <c r="E2">
         <v>45</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>501</v>
       </c>
@@ -484,8 +509,11 @@
       <c r="E3">
         <v>45</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>502</v>
       </c>
@@ -501,8 +529,11 @@
       <c r="E4">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>503</v>
       </c>
@@ -518,8 +549,11 @@
       <c r="E5">
         <v>45</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>504</v>
       </c>
@@ -535,8 +569,11 @@
       <c r="E6">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>505</v>
       </c>
@@ -552,8 +589,11 @@
       <c r="E7">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>506</v>
       </c>
@@ -569,8 +609,11 @@
       <c r="E8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>507</v>
       </c>
@@ -586,8 +629,11 @@
       <c r="E9">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>508</v>
       </c>
@@ -603,8 +649,11 @@
       <c r="E10">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>509</v>
       </c>
@@ -620,8 +669,11 @@
       <c r="E11">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>510</v>
       </c>
@@ -637,8 +689,11 @@
       <c r="E12">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>511</v>
       </c>
@@ -654,8 +709,11 @@
       <c r="E13">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>512</v>
       </c>
@@ -671,8 +729,11 @@
       <c r="E14">
         <v>30</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>513</v>
       </c>
@@ -688,8 +749,11 @@
       <c r="E15">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>514</v>
       </c>
@@ -705,8 +769,11 @@
       <c r="E16">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>515</v>
       </c>
@@ -722,8 +789,11 @@
       <c r="E17">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>516</v>
       </c>
@@ -739,8 +809,11 @@
       <c r="E18">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>517</v>
       </c>
@@ -756,8 +829,11 @@
       <c r="E19">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>518</v>
       </c>
@@ -773,8 +849,11 @@
       <c r="E20">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>519</v>
       </c>
@@ -790,8 +869,11 @@
       <c r="E21">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>520</v>
       </c>
@@ -807,8 +889,11 @@
       <c r="E22">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>521</v>
       </c>
@@ -824,8 +909,11 @@
       <c r="E23">
         <v>20</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>522</v>
       </c>
@@ -841,8 +929,11 @@
       <c r="E24">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>523</v>
       </c>
@@ -858,8 +949,11 @@
       <c r="E25">
         <v>20</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>524</v>
       </c>
@@ -875,8 +969,11 @@
       <c r="E26">
         <v>20</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>525</v>
       </c>
@@ -892,8 +989,11 @@
       <c r="E27">
         <v>30</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>526</v>
       </c>
@@ -909,8 +1009,11 @@
       <c r="E28">
         <v>30</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>527</v>
       </c>
@@ -926,8 +1029,11 @@
       <c r="E29">
         <v>30</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>528</v>
       </c>
@@ -943,8 +1049,11 @@
       <c r="E30">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>529</v>
       </c>
@@ -960,8 +1069,11 @@
       <c r="E31">
         <v>50</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>530</v>
       </c>
@@ -976,6 +1088,128 @@
       </c>
       <c r="E32">
         <v>50</v>
+      </c>
+      <c r="F32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>531</v>
+      </c>
+      <c r="B33">
+        <v>4.5</v>
+      </c>
+      <c r="C33">
+        <v>1.2</v>
+      </c>
+      <c r="D33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>532</v>
+      </c>
+      <c r="B34">
+        <v>4.5</v>
+      </c>
+      <c r="C34">
+        <v>1.2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>533</v>
+      </c>
+      <c r="B35">
+        <v>4.5</v>
+      </c>
+      <c r="C35">
+        <v>1.2</v>
+      </c>
+      <c r="D35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>534</v>
+      </c>
+      <c r="B36">
+        <v>4.5</v>
+      </c>
+      <c r="C36">
+        <v>1.2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>535</v>
+      </c>
+      <c r="B37">
+        <v>4.5</v>
+      </c>
+      <c r="C37">
+        <v>1.2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>536</v>
+      </c>
+      <c r="B38">
+        <v>4.5</v>
+      </c>
+      <c r="C38">
+        <v>1.2</v>
+      </c>
+      <c r="D38" t="s">
+        <v>4</v>
+      </c>
+      <c r="F38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>537</v>
+      </c>
+      <c r="B39">
+        <v>4.5</v>
+      </c>
+      <c r="C39">
+        <v>1.2</v>
+      </c>
+      <c r="D39" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
